--- a/benchmark/generated_files/RIC-2_M_019.xlsx
+++ b/benchmark/generated_files/RIC-2_M_019.xlsx
@@ -485,11 +485,11 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 18,00 EUR DEL 01.01.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 18,86 EUR DEL 01.01.2026 A (ITA) SUSHI SHOP CAGLIARI</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>18</v>
+        <v>18.86</v>
       </c>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="inlineStr">
@@ -500,20 +500,20 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 8612 ESSELUNGA S.P.A.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>123.87</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n">
+        <v>298.49</v>
+      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -522,20 +522,20 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,83 EUR DEL 02.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="E4" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n">
+        <v>214.04</v>
+      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -544,18 +544,18 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7.73</v>
+        <v>9.41</v>
       </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
@@ -566,20 +566,20 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n">
-        <v>69.36</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 119,03 EUR DEL 05.01.2026 A (ITA) CONAD CITY ROMA</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>119.03</v>
+      </c>
+      <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -588,20 +588,20 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>46027</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n">
-        <v>110.5</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 57,14 EUR DEL 05.01.2026 A (ITA) VALMANO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -610,18 +610,18 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>46028</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 5,38 EUR DEL 06.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 54,01 EUR DEL 05.01.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5.38</v>
+        <v>54.01</v>
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="inlineStr">
@@ -639,13 +639,13 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0123456</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n">
-        <v>88.69</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 36,79 EUR DEL 06.01.2026 A (ITA) VALMANO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -654,20 +654,20 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46031</v>
+        <v>46028</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 43,83 EUR DEL 07.01.2026 A (ITA) BAR CENTRALE</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>43.83</v>
-      </c>
-      <c r="E10" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n">
+        <v>246.8</v>
+      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -683,11 +683,11 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 51,63 EUR DEL 07.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 32,48 EUR DEL 07.01.2026 A (ITA) VALMANO TORINO</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>51.63</v>
+        <v>32.48</v>
       </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="inlineStr">
@@ -698,18 +698,18 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 56,22 EUR DEL 08.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Addebito SDD - JUST EAT ITALY SRL</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>56.22</v>
+        <v>26.33</v>
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="inlineStr">
@@ -720,18 +720,18 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 8,00 EUR DEL 08.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-217678370</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="inlineStr">
@@ -745,17 +745,17 @@
         <v>46030</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46030</v>
+        <v>46032</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n">
-        <v>136.25</v>
-      </c>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2448 GIAP</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -764,20 +764,20 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46031</v>
+        <v>46033</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 32,47 EUR DEL 09.01.2026 A (ITA) STAZIONE Q8</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>32.47</v>
-      </c>
-      <c r="E15" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n">
+        <v>288.69</v>
+      </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -786,20 +786,20 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0123456</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n">
-        <v>205.41</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 28,11 EUR DEL 11.01.2026 A (ITA) HISTOIRE D'OR</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -811,15 +811,15 @@
         <v>46034</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 84,31 EUR DEL 12.01.2026 A (ITA) TRENITALIA S.P.A.</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>84.31</v>
+        <v>14.58</v>
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="inlineStr">
@@ -837,13 +837,13 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 90,37 EUR DEL 13.01.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>90.37</v>
-      </c>
-      <c r="E18" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n">
+        <v>156.37</v>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -855,17 +855,17 @@
         <v>46036</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0123456</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n">
-        <v>121.46</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 29,34 EUR DEL 14.01.2026 A (ITA) LA PIADINERIA</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -874,18 +874,18 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46039</v>
+        <v>46036</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 47,27 EUR DEL 17.01.2026 A (ITA) ITALO NTV S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 80,21 EUR DEL 14.01.2026 A (ITA) BREWDOG SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>47.27</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="inlineStr">
@@ -896,18 +896,18 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46039</v>
+        <v>46036</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9937 CARREFOUR CONTACT TORINO</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>172.6</v>
       </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="inlineStr">
@@ -918,18 +918,18 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46040</v>
+        <v>46037</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46040</v>
+        <v>46037</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>Pagam. POS - PAGAMENTO POS 51,07 EUR DEL 15.01.2026 A (ITA) ALL'ANTICO VINAIO VOMERO</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.64</v>
+        <v>51.07</v>
       </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="inlineStr">
@@ -940,18 +940,18 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>46040</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 5,19 EUR DEL 18.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1242 GNP VENEZIA</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.19</v>
+        <v>43.73</v>
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="inlineStr">
@@ -965,15 +965,15 @@
         <v>46040</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Pagam. POS - PAGAMENTO POS 72,07 EUR DEL 18.01.2026 A (ITA) BAR CENTRALE</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>35.08</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="inlineStr">
@@ -984,18 +984,18 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>46042</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 47,50 EUR DEL 20.01.2026 A (ITA) KEROPETROL</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>39.09</v>
+        <v>47.5</v>
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="inlineStr">
@@ -1006,18 +1006,18 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 71,32 EUR DEL 19.01.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>71.31999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="inlineStr">
@@ -1028,7 +1028,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>46042</v>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n">
-        <v>77.5</v>
+        <v>272.04</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -1050,18 +1050,18 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46042</v>
+        <v>46045</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 1124 LIDL ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 10,95 EUR DEL 23.01.2026 A (ITA) VALMANO</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>99.44</v>
+        <v>10.95</v>
       </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="inlineStr">
@@ -1072,18 +1072,18 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>8.76</v>
+        <v>12.84</v>
       </c>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="inlineStr">
@@ -1094,18 +1094,18 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46045</v>
+        <v>46047</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46047</v>
+        <v>46049</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 70,02 EUR DEL 23.01.2026 A (ITA) TRENITALIA S.P.A.</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-210777742</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>70.02</v>
+        <v>6.39</v>
       </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="inlineStr">
@@ -1116,18 +1116,18 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 79,22 EUR DEL 24.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 77,03 EUR DEL 26.01.2026 A (ITA) ENILIVE</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>79.22</v>
+        <v>77.03</v>
       </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="inlineStr">
@@ -1138,20 +1138,20 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>46048</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="E32" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n">
+        <v>293.83</v>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1167,11 +1167,11 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 69,83 EUR DEL 27.01.2026 A (ITA) STAZIONE Q8</t>
+          <t>Pagam. POS - PAGAMENTO POS 44,32 EUR DEL 27.01.2026 A (ITA) TABACCHERIA N.12</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>69.83</v>
+        <v>44.32</v>
       </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="inlineStr">
@@ -1182,18 +1182,18 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Pagam. POS - PAGAMENTO POS 148,10 EUR DEL 28.01.2026 A (ITA) ESSELUNGA MILANO</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>7.28</v>
+        <v>148.1</v>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="inlineStr">
@@ -1211,11 +1211,11 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 13,65 EUR DEL 29.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>Pagam. POS - PAGAMENTO POS 35,05 EUR DEL 29.01.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>13.65</v>
+        <v>35.05</v>
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="inlineStr">
@@ -1226,18 +1226,18 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46051</v>
+        <v>46053</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 10,55 EUR DEL 29.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 12,54 EUR DEL 31.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>10.55</v>
+        <v>12.54</v>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="inlineStr">
@@ -1248,18 +1248,18 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 98,16 EUR DEL 30.01.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 12,91 EUR DEL 02.02.2026 A (ITA) THUN</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>98.16</v>
+        <v>12.91</v>
       </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="inlineStr">
@@ -1270,19 +1270,19 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46052</v>
+        <v>46057</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
         </is>
       </c>
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n">
-        <v>138.07</v>
+        <v>263.3</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -1292,18 +1292,18 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46053</v>
+        <v>46058</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 64,20 EUR DEL 31.01.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>64.2</v>
+        <v>7.02</v>
       </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="inlineStr">
@@ -1314,18 +1314,18 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46054</v>
+        <v>46059</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46055</v>
+        <v>46060</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>45.65</v>
+        <v>10.49</v>
       </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="inlineStr">
@@ -1336,18 +1336,18 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46054</v>
+        <v>46060</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46056</v>
+        <v>46060</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 132,49 EUR DEL 01.02.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>132.49</v>
+        <v>12.81</v>
       </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="inlineStr">
@@ -1358,18 +1358,18 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46055</v>
+        <v>46060</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46055</v>
+        <v>46060</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 58,48 EUR DEL 02.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>Pagam. POS - PAGAMENTO POS 95,32 EUR DEL 07.02.2026 A (ITA) PRIMOR</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>58.48</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="inlineStr">
@@ -1380,20 +1380,20 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46056</v>
+        <v>46063</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46057</v>
+        <v>46065</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0123456</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n">
-        <v>118.61</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 50,78 EUR DEL 10.02.2026 A (ITA) OLD WILD WEST</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>50.78</v>
+      </c>
+      <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1402,18 +1402,18 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46058</v>
+        <v>46065</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>Pagam. POS - PAGAMENTO POS 84,75 EUR DEL 10.02.2026 A (ITA) RISTORANTE DA GINO</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>84.75</v>
       </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="inlineStr">
@@ -1424,18 +1424,18 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9225 BILLY TACOS VOMERO</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>35.7</v>
+        <v>39.84</v>
       </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="inlineStr">
@@ -1446,18 +1446,18 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46059</v>
+        <v>46068</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 7,38 EUR DEL 06.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4746 WYCON COSMETICS FUORIGROTTA</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>7.38</v>
+        <v>29.3</v>
       </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="inlineStr">
@@ -1468,18 +1468,18 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46062</v>
+        <v>46067</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Pagam. POS - PAGAMENTO POS 7,05 EUR DEL 13.02.2026 A (ITA) MCDONALD'S ITALIA</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>73.91</v>
+        <v>7.05</v>
       </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="inlineStr">
@@ -1490,18 +1490,18 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46062</v>
+        <v>46067</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46064</v>
+        <v>46069</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 126,58 EUR DEL 14.02.2026 A (ITA) LIDL ITALIA SRL</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10.69</v>
+        <v>126.58</v>
       </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="inlineStr">
@@ -1512,20 +1512,20 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46063</v>
+        <v>46069</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0123456</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n">
-        <v>75.78</v>
-      </c>
+          <t>Addebito SDD - SPOTIFY AB</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1534,20 +1534,20 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46063</v>
+        <v>46069</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 16,05 EUR DEL 10.02.2026 A (ITA) RISTORANTE DA GINO</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>16.05</v>
-      </c>
-      <c r="E50" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n">
+        <v>288.75</v>
+      </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1556,18 +1556,18 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46065</v>
+        <v>46071</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 32,19 EUR DEL 12.02.2026 A (ITA) PANIFICIO TOSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 25,34 EUR DEL 17.02.2026 A (ITA) SUSHI SHOP</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>32.19</v>
+        <v>25.34</v>
       </c>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="inlineStr">
@@ -1578,18 +1578,18 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46068</v>
+        <v>46070</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 103,54 EUR DEL 13.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 78,09 EUR DEL 17.02.2026 A (ITA) TAMOIL</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>103.54</v>
+        <v>78.09</v>
       </c>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="inlineStr">
@@ -1600,18 +1600,18 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 40,96 EUR DEL 16.02.2026 A (ITA) BAR CENTRALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 10,88 EUR DEL 17.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>40.96</v>
+        <v>10.88</v>
       </c>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="inlineStr">
@@ -1629,11 +1629,11 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 7,44 EUR DEL 17.02.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>7.44</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="inlineStr">
@@ -1651,13 +1651,13 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 49,17 EUR DEL 17.02.2026 A (ITA) DISTRIBUTORE ENI</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>49.17</v>
-      </c>
-      <c r="E55" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n">
+        <v>269.04</v>
+      </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1673,11 +1673,11 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-219192503</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>7.72</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="inlineStr">
@@ -1691,15 +1691,15 @@
         <v>46071</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46073</v>
+        <v>46071</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 7,12 EUR DEL 18.02.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 160,98 EUR DEL 18.02.2026 A (ITA) SÌ CON TE VENEZIA</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>7.12</v>
+        <v>160.98</v>
       </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="inlineStr">
@@ -1710,18 +1710,18 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46074</v>
+        <v>46071</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46074</v>
+        <v>46072</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 101,43 EUR DEL 21.02.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 5,80 EUR DEL 18.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>101.43</v>
+        <v>5.8</v>
       </c>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="inlineStr">
@@ -1732,18 +1732,18 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46074</v>
+        <v>46072</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46074</v>
+        <v>46072</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6538 VALMANO CORSICO</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>14.09</v>
+        <v>99.28</v>
       </c>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="inlineStr">
@@ -1754,18 +1754,18 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46075</v>
+        <v>46073</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46075</v>
+        <v>46073</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>5.07</v>
+        <v>6</v>
       </c>
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="inlineStr">
@@ -1776,18 +1776,18 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-219220514</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>5.47</v>
+        <v>8.76</v>
       </c>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="inlineStr">
@@ -1798,18 +1798,18 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 28,28 EUR DEL 23.02.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>28.28</v>
+        <v>12.2</v>
       </c>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="inlineStr">
@@ -1820,18 +1820,18 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46078</v>
+        <v>46074</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Pagam. POS - PAGAMENTO POS 7,07 EUR DEL 21.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>9.66</v>
+        <v>7.07</v>
       </c>
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="inlineStr">
@@ -1842,18 +1842,18 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B64" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="B64" s="2" t="n">
-        <v>46079</v>
-      </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 36,59 EUR DEL 24.02.2026 A (ITA) DISTRIBUTORE ENI</t>
+          <t>Pagam. POS - PAGAMENTO POS 19,97 EUR DEL 22.02.2026 A (ITA) BILLY TACOS EUR</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>36.59</v>
+        <v>19.97</v>
       </c>
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="inlineStr">
@@ -1864,18 +1864,18 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46077</v>
+        <v>46075</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46077</v>
+        <v>46075</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 60,17 EUR DEL 24.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 30,35 EUR DEL 22.02.2026 A (ITA) 100 MONTADITOS PORTA NUOVA</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>60.17</v>
+        <v>30.35</v>
       </c>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="inlineStr">
@@ -1886,18 +1886,18 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>61.98</v>
+        <v>17.16</v>
       </c>
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="inlineStr">
@@ -1908,18 +1908,18 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46081</v>
+        <v>46078</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 20,84 EUR DEL 23.02.2026 A (ITA) ROSSOPOMODORO PORTA NUOVA</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>20.84</v>
       </c>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="inlineStr">
@@ -1930,20 +1930,20 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46080</v>
+        <v>46076</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,36 EUR DEL 27.02.2026 A (ITA) UNIEURO S.P.A.</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="E68" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n">
+        <v>101.35</v>
+      </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1952,18 +1952,18 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELEPASS S.P.A. PEDAGGI</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-215360590</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>56.09</v>
+        <v>6.36</v>
       </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="inlineStr">
@@ -1977,17 +1977,17 @@
         <v>46080</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n">
-        <v>68.95999999999999</v>
-      </c>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2182 TUODÌ TIBURTINA</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="E70" s="3" t="n"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
